--- a/league_dict.xlsx
+++ b/league_dict.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/557e8c8e9b1f0372/Documents/WT Analysis/Excel Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{5EAC5B0D-B715-4733-8BC4-0749D208B439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76B34D2B-FD9E-4428-867E-C018B5492FE8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C16683-C2E1-421C-8891-320EFF77A7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E870964E-72B7-432A-AC57-81E8B1FB7B9A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="81">
   <si>
     <t>Season</t>
   </si>
@@ -264,6 +264,21 @@
   </si>
   <si>
     <t>aouykkl1rt7zo06sg0kbzkbh0</t>
+  </si>
+  <si>
+    <t>J-League</t>
+  </si>
+  <si>
+    <t>Allsvenskan</t>
+  </si>
+  <si>
+    <t>b99u9gpztyjs5u1i88z6qvg9g</t>
+  </si>
+  <si>
+    <t>6zkfyunc0lfteytfj6slonuhg</t>
+  </si>
+  <si>
+    <t>82kx7v6msx3ibpmifw6nxurys</t>
   </si>
 </sst>
 </file>
@@ -322,10 +337,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -645,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673AED86-F034-49DA-B6EF-799C1DFCCB2C}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -1160,6 +1171,39 @@
         <v>75</v>
       </c>
     </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2026</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2026</v>
+      </c>
+      <c r="B40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2026</v>
+      </c>
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/league_dict.xlsx
+++ b/league_dict.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C16683-C2E1-421C-8891-320EFF77A7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8140BD0B-909A-4879-B1B8-9AF449A81F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E870964E-72B7-432A-AC57-81E8B1FB7B9A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E870964E-72B7-432A-AC57-81E8B1FB7B9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
   <si>
     <t>Season</t>
   </si>
@@ -107,12 +107,6 @@
     <t>Austrian Bundesliga</t>
   </si>
   <si>
-    <t>Brasilerao</t>
-  </si>
-  <si>
-    <t>MLS</t>
-  </si>
-  <si>
     <t>Champions League</t>
   </si>
   <si>
@@ -125,81 +119,6 @@
     <t>Pro League</t>
   </si>
   <si>
-    <t>51r6ph2woavlbbpk8f29nynf8</t>
-  </si>
-  <si>
-    <t>2025/26</t>
-  </si>
-  <si>
-    <t>bmmk637l2a33h90zlu36kx8no</t>
-  </si>
-  <si>
-    <t>5as0oqxeagsuzyf75xm7p5jbo</t>
-  </si>
-  <si>
-    <t>1fupi48urd1qk7t1rj12eyxw4</t>
-  </si>
-  <si>
-    <t>461lceqlslg7w32yc4w0ogems</t>
-  </si>
-  <si>
-    <t>6lhltebj0dx79xptn0hyph5as</t>
-  </si>
-  <si>
-    <t>87b2o38m190egljltsudvz7ys</t>
-  </si>
-  <si>
-    <t>3zoeegue4xtul58c8ksahcjdg</t>
-  </si>
-  <si>
-    <t>80zg2v1cuqcfhphn56u4qpyqc</t>
-  </si>
-  <si>
-    <t>dko0hzifl1xv9c51s3ai017v8</t>
-  </si>
-  <si>
-    <t>dbxs75cag7zyip5re0ppsanmc</t>
-  </si>
-  <si>
-    <t>f12tw9djrb2bvlzrtg4hhme50</t>
-  </si>
-  <si>
-    <t>2bchmrj23l9u42d68ntcekob8</t>
-  </si>
-  <si>
-    <t>3mjmai3idiul01s8jm0g7x6hg</t>
-  </si>
-  <si>
-    <t>7l4z25o4hc0fmj9rdspcisdn8</t>
-  </si>
-  <si>
-    <t>bfxnqtcsy92klp10rbwikb47o</t>
-  </si>
-  <si>
-    <t>emdmtfr1v8rey2qru3xzfwges</t>
-  </si>
-  <si>
-    <t>6evrk16rq1mhn0eajdk0bvehg</t>
-  </si>
-  <si>
-    <t>d5ju52a9misru35821zuqysd0</t>
-  </si>
-  <si>
-    <t>4jr49qim3gv5bjx3wjkf6n0us</t>
-  </si>
-  <si>
-    <t>9pqtmpr3w8jm73y0eb8hmum8k</t>
-  </si>
-  <si>
-    <t>2p9ipxt6ftkdphe5afitgd0</t>
-  </si>
-  <si>
-    <t>16lkdpoccbh056r0v0bordo2c</t>
-  </si>
-  <si>
-    <t>2mr0u0l78k2gdsm79q56tb2fo</t>
-  </si>
-  <si>
     <t>7ttpe5jzya3vjhjadiemjy7mc</t>
   </si>
   <si>
@@ -218,27 +137,12 @@
     <t>Superligaen</t>
   </si>
   <si>
-    <t>3o8l1yf2irp018eaa2far455g</t>
-  </si>
-  <si>
-    <t>f2s3v11z1occwbp69h73coqvo</t>
-  </si>
-  <si>
-    <t>Club World Cup</t>
-  </si>
-  <si>
-    <t>7n3ltxz65zjcd8z9eyr5i2wb8</t>
-  </si>
-  <si>
     <t>Europa League Qualifiers</t>
   </si>
   <si>
     <t>Europa Conference League Qualifiers</t>
   </si>
   <si>
-    <t>9r8h2z7y89a0h1995f4bz105w</t>
-  </si>
-  <si>
     <t>Friendly</t>
   </si>
   <si>
@@ -251,21 +155,9 @@
     <t>UEFA Super Cup</t>
   </si>
   <si>
-    <t>db8f4sqdf7s0g850fspnf8hlg</t>
-  </si>
-  <si>
-    <t>ceu82myq9rpq841ts3jl7uvis</t>
-  </si>
-  <si>
-    <t>SWPL</t>
-  </si>
-  <si>
     <t>Eredivisie</t>
   </si>
   <si>
-    <t>aouykkl1rt7zo06sg0kbzkbh0</t>
-  </si>
-  <si>
     <t>J-League</t>
   </si>
   <si>
@@ -279,6 +171,111 @@
   </si>
   <si>
     <t>82kx7v6msx3ibpmifw6nxurys</t>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>99jev9kv55deht65t6myggxlg</t>
+  </si>
+  <si>
+    <t>1rpi0q64a7kut2wiuvecmgbv8</t>
+  </si>
+  <si>
+    <t>acatl9aedc5l4im3r8l890y6s</t>
+  </si>
+  <si>
+    <t>94e2tqj0lcfsmhmbk75knn310</t>
+  </si>
+  <si>
+    <t>7xwajracalkvgn9iva5wah3is</t>
+  </si>
+  <si>
+    <t>6pdwluctev9iebv00r4qqukno</t>
+  </si>
+  <si>
+    <t>al48ooi8acoibema226051250</t>
+  </si>
+  <si>
+    <t>b7amy99ea2lpnx81o6q94pst0</t>
+  </si>
+  <si>
+    <t>7kjvvls20hnhjguys4t73yjh0</t>
+  </si>
+  <si>
+    <t>75p5723yryew2ywn0isvf7cic</t>
+  </si>
+  <si>
+    <t>dap7q17azs3j8a5sv36enfr4k</t>
+  </si>
+  <si>
+    <t>830epggffy1nfkfyrtpqdwhlg</t>
+  </si>
+  <si>
+    <t>fgkxmpz2ewao1l63jrbkgg7o</t>
+  </si>
+  <si>
+    <t>bqnc4ccgnrp6pb3bktqet0yz8</t>
+  </si>
+  <si>
+    <t>b4rd8q7zjvernie5778azl7v8</t>
+  </si>
+  <si>
+    <t>8h5xijv2u4mlf5028gso6kw7o</t>
+  </si>
+  <si>
+    <t>c21j57b4gkcp8rzyp2cn8jbpw</t>
+  </si>
+  <si>
+    <t>60cryos85i4bp5ul34tt0brx0</t>
+  </si>
+  <si>
+    <t>2aad86jp2iq9zr22oxib5a4gk</t>
+  </si>
+  <si>
+    <t>1ypt1hmmrdjdek7yieatpskyc</t>
+  </si>
+  <si>
+    <t>5ysazl26p4ksxbonjpbamevpw</t>
+  </si>
+  <si>
+    <t>aa2sqzvq68621ok3nca8csrh0</t>
+  </si>
+  <si>
+    <t>13prgjp0qzce661j00a3jy3o4</t>
+  </si>
+  <si>
+    <t>32gy6t29t9240sgu7l11j9nh0</t>
+  </si>
+  <si>
+    <t>Veikkausliiga</t>
+  </si>
+  <si>
+    <t>56cvval3nf96u0bf9rzs9h6vo</t>
+  </si>
+  <si>
+    <t>7bdyxkrzt42tv7377rpz5nqc4</t>
+  </si>
+  <si>
+    <t>Eerste Divisie</t>
+  </si>
+  <si>
+    <t>1ztoqmkrzy1d4ejf5jokthiqc</t>
+  </si>
+  <si>
+    <t>beev3xu6oz7vc6l4rcxygw4d0</t>
+  </si>
+  <si>
+    <t>Eliteserien</t>
+  </si>
+  <si>
+    <t>a8xa8yfi2tlljxrwyxcst51xw</t>
+  </si>
+  <si>
+    <t>cx0b7yl7kqmgay9wn2c3zyjh0</t>
+  </si>
+  <si>
+    <t>7qmc7ue3f8yzv8yqmsxc9irro</t>
   </si>
 </sst>
 </file>
@@ -656,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673AED86-F034-49DA-B6EF-799C1DFCCB2C}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -674,18 +671,18 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>47</v>
@@ -693,13 +690,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>48</v>
@@ -707,13 +704,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>108</v>
@@ -721,13 +718,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D5">
         <v>109</v>
@@ -735,13 +732,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>132</v>
@@ -749,13 +746,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D7">
         <v>133</v>
@@ -763,445 +760,411 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2025</v>
+      <c r="A9" t="s">
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>126</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>59</v>
+      </c>
+      <c r="D11">
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>61</v>
+      </c>
+      <c r="D13">
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D14">
-        <v>54</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="D15">
-        <v>146</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>63</v>
+      </c>
+      <c r="D17">
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>78</v>
+      </c>
+      <c r="D19">
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D20">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D21">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2025</v>
+      <c r="A22" t="s">
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D22">
-        <v>268</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2025</v>
+      <c r="A23" t="s">
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D23">
-        <v>130</v>
+        <v>10216</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D24">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="B25" t="s">
-        <v>26</v>
-      </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D25">
-        <v>73</v>
+        <v>10611</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D26">
-        <v>10216</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D27">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D28">
-        <v>10611</v>
+        <v>10613</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D29">
-        <v>113</v>
+        <v>10615</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
+      <c r="A30">
+        <v>2026</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D31">
-        <v>78</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>30</v>
+      <c r="A32">
+        <v>2026</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32">
-        <v>10613</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33">
-        <v>10615</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2026</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2026</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
         <v>69</v>
       </c>
-      <c r="C35" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>2025</v>
-      </c>
-      <c r="B36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2026</v>
+      </c>
+      <c r="B38" t="s">
         <v>73</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2026</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>2026</v>
-      </c>
-      <c r="B40" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2026</v>
-      </c>
-      <c r="B41" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
